--- a/src/src/main/webapp/portal/asset/info/APM_Asset_Modify_History_List.xlsx
+++ b/src/src/main/webapp/portal/asset/info/APM_Asset_Modify_History_List.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6906B34D-3661-4DE2-9269-E2815DD20818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D339662-4019-4FB7-A36E-0BD539DB6A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ImportFilesList" sheetId="1" r:id="rId1"/>
+    <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/src/src/main/webapp/portal/asset/info/APM_Asset_Modify_History_List.xlsx
+++ b/src/src/main/webapp/portal/asset/info/APM_Asset_Modify_History_List.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D339662-4019-4FB7-A36E-0BD539DB6A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8388C2-D015-4894-853B-69CEB08276D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>资产名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,6 +59,114 @@
   </si>
   <si>
     <t>是否在用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产处置结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>采购日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>采购价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二维码(旧)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二维码(新)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启用日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设备型号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出厂日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修负责人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制造商</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品牌/制造商简称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注册编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>供应商</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>医疗器械分类(旧)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>医疗器械子分类(旧)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制造商序列号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用年限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>质保截止日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用途分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资金来源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计量等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风险等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否急救设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否进口设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>医疗器械分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -384,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.88671875" customWidth="1"/>
@@ -392,13 +500,16 @@
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="18.77734375" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="7" width="15.5546875" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" customWidth="1"/>
+    <col min="6" max="14" width="15.5546875" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" customWidth="1"/>
+    <col min="16" max="16" width="13.88671875" customWidth="1"/>
+    <col min="17" max="17" width="12.88671875" customWidth="1"/>
+    <col min="22" max="22" width="10.21875" customWidth="1"/>
+    <col min="25" max="25" width="12.88671875" customWidth="1"/>
+    <col min="26" max="35" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -418,20 +529,102 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="O1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="P1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
         <v>9</v>
+      </c>
+      <c r="R1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" t="s">
+        <v>12</v>
+      </c>
+      <c r="U1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V1" t="s">
+        <v>14</v>
+      </c>
+      <c r="W1" t="s">
+        <v>15</v>
+      </c>
+      <c r="X1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>